--- a/data/template_dataset.xlsx
+++ b/data/template_dataset.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/Meta_Methods_UAlberta/effect_size_tutorial/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6B10D4-2845-9847-B65A-A9657BE932F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A67705-2C17-094E-A569-30A06C2791E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{DB434A4E-2740-E445-AC13-19792B9677B5}"/>
   </bookViews>
   <sheets>
-    <sheet name="metadata" sheetId="4" r:id="rId1"/>
+    <sheet name="Column descriptions" sheetId="4" r:id="rId1"/>
     <sheet name="SMD or lnRoM" sheetId="1" r:id="rId2"/>
     <sheet name="lnOR or lnRR" sheetId="2" r:id="rId3"/>
     <sheet name="Zr" sheetId="3" r:id="rId4"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="105">
   <si>
     <t>doi</t>
   </si>
@@ -340,8 +340,36 @@
     <t>The value of the correlation coefficient</t>
   </si>
   <si>
+    <t>summarized_across</t>
+  </si>
+  <si>
+    <t>Are the data summaries (mean, error) across spatially distinct individuals or sites, across temporal measurements of the same individuals or sites, or across both?</t>
+  </si>
+  <si>
+    <t>spatial, temporal, spatiotemporal</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">These columns describe the bibliometric data for the article, the location in the article from which the data was extracted, IDs to control for non-independence </t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Optional with Zr—only applies to correlations based on mean±error. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>Are the data summaries (mean, error) across spatially distinct individuals or sites, across temporal measurements of the same individuals or sites, or across both?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">These columns describe the bibliometric data for the article, the location in the article from which the data was extracted, and IDs to control for non-independence </t>
     </r>
     <r>
       <rPr>
@@ -572,7 +600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -627,17 +655,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -646,7 +664,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -669,12 +687,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -990,112 +1017,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4CE9E0-C701-AD41-BC6C-4A671B2C8E8B}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" style="44" customWidth="1"/>
-    <col min="2" max="2" width="67.6640625" style="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.1640625" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="43"/>
-    <col min="5" max="16384" width="10.83203125" style="44"/>
+    <col min="1" max="1" width="25.83203125" style="42" customWidth="1"/>
+    <col min="2" max="2" width="67.6640625" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.1640625" style="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="42"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
     </row>
     <row r="2" spans="1:4" ht="83" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
+      <c r="A2" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="43" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="51"/>
+      <c r="D4" s="47"/>
     </row>
     <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="51"/>
+      <c r="D5" s="47"/>
     </row>
     <row r="6" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="51" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="51"/>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="47"/>
     </row>
     <row r="8" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="51"/>
+      <c r="D8" s="47"/>
     </row>
     <row r="9" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="47"/>
     </row>
     <row r="10" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
@@ -1107,95 +1133,95 @@
       <c r="C10" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="51"/>
+      <c r="D10" s="47"/>
     </row>
     <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="56" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="51"/>
+      <c r="D11" s="47"/>
     </row>
     <row r="13" spans="1:4" ht="32" x14ac:dyDescent="0.4">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
     </row>
     <row r="14" spans="1:4" ht="97" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-    </row>
-    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+    </row>
+    <row r="15" spans="1:4" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B16" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C16" s="33" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+    <row r="17" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B17" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C17" s="33" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B19" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C19" s="34" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="23" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C20" s="35" t="s">
         <v>65</v>
@@ -1203,32 +1229,32 @@
     </row>
     <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B22" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C22" s="35" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>65</v>
@@ -1236,251 +1262,273 @@
     </row>
     <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="36" t="s">
+      <c r="B25" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C25" s="36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="38" t="s">
+    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B26" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C26" s="39" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="32" x14ac:dyDescent="0.4">
-      <c r="A29" s="62" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.4">
+      <c r="A30" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-    </row>
-    <row r="30" spans="1:3" ht="74" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="45" t="s">
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+    </row>
+    <row r="31" spans="1:3" ht="74" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="23" t="s">
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+    </row>
+    <row r="32" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B33" s="31" t="s">
         <v>80</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>82</v>
       </c>
       <c r="C33" s="31" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="24" t="s">
-        <v>19</v>
+      <c r="A34" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C34" s="31" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="32" x14ac:dyDescent="0.4">
-      <c r="A36" s="62" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.4">
+      <c r="A38" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="62"/>
-      <c r="C36" s="62"/>
-    </row>
-    <row r="37" spans="1:3" ht="116" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="45" t="s">
+      <c r="B38" s="60"/>
+      <c r="C38" s="60"/>
+    </row>
+    <row r="39" spans="1:3" ht="116" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-    </row>
-    <row r="38" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A38" s="63" t="s">
+      <c r="B39" s="62"/>
+      <c r="C39" s="62"/>
+    </row>
+    <row r="40" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A40" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="64" t="s">
+      <c r="B40" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="64" t="s">
+      <c r="C40" s="59" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="22" t="s">
+    <row r="41" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="34" t="s">
+      <c r="B41" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C41" s="34" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A40" s="22" t="s">
+    <row r="42" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B42" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C42" s="34" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A41" s="23" t="s">
+    <row r="43" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A43" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="35" t="s">
+      <c r="B43" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="35" t="s">
+      <c r="C43" s="35" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A42" s="23" t="s">
+    <row r="44" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A44" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="35" t="s">
+      <c r="B44" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="35" t="s">
+      <c r="C44" s="35" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="23" t="s">
+    <row r="45" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A45" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B43" s="35" t="s">
+      <c r="B45" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C45" s="35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A44" s="24" t="s">
+    <row r="46" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A46" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="36" t="s">
+      <c r="B46" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="36" t="s">
+      <c r="C46" s="36" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A45" s="24" t="s">
+    <row r="47" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A47" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="36" t="s">
+      <c r="B47" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="C47" s="36" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="24" t="s">
+    <row r="48" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="36" t="s">
+      <c r="B48" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C48" s="36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A47" s="19" t="s">
+    <row r="49" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A49" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="37" t="s">
+      <c r="B49" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="37" t="s">
+      <c r="C49" s="37" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="19" t="s">
+    <row r="50" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A50" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="37" t="s">
+      <c r="B50" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="37" t="s">
+      <c r="C50" s="37" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1488,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D8913A-2DED-E14B-8F03-74C552774659}">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="26" bestFit="1" customWidth="1"/>
@@ -1499,22 +1547,23 @@
     <col min="6" max="6" width="27.5" style="28" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.5" style="29" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.1640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.1640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.1640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.83203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8" style="41" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="10.83203125" style="41"/>
-    <col min="22" max="16384" width="10.83203125" style="25"/>
+    <col min="9" max="9" width="20" style="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" style="30" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.1640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.83203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" style="41" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.83203125" style="41"/>
+    <col min="23" max="16384" width="10.83203125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1540,42 +1589,45 @@
         <v>8</v>
       </c>
       <c r="I1" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="K1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="L1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="N1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="O1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="P1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="Q1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="24" t="s">
+      <c r="R1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="S1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="38" t="s">
+      <c r="T1" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="40" t="s">
+      <c r="U1" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="40" t="s">
+      <c r="V1" s="40" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1648,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE480F93-F175-7D41-991D-CD4250D6164F}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="9" bestFit="1" customWidth="1"/>
@@ -1659,20 +1711,21 @@
     <col min="6" max="6" width="24.5" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.5" style="12" customWidth="1"/>
-    <col min="9" max="9" width="24.5" style="17" customWidth="1"/>
-    <col min="10" max="10" width="10.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" style="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18" style="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18" style="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="10.83203125" style="10"/>
-    <col min="20" max="16384" width="10.83203125" style="8"/>
+    <col min="9" max="9" width="24.5" style="21" customWidth="1"/>
+    <col min="10" max="10" width="24.5" style="17" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.83203125" style="10"/>
+    <col min="21" max="16384" width="10.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1697,37 +1750,40 @@
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>29</v>
       </c>
     </row>

--- a/data/template_dataset.xlsx
+++ b/data/template_dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/Meta_Methods_UAlberta/effect_size_tutorial/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A67705-2C17-094E-A569-30A06C2791E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150EC6A2-96D6-0D47-B125-B1858D05264F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{DB434A4E-2740-E445-AC13-19792B9677B5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="111">
   <si>
     <t>doi</t>
   </si>
@@ -388,6 +388,24 @@
       </rPr>
       <t xml:space="preserve"> articles. "Measurement_scale" is an optional column pertaining to vegetation data. Unit of replication should always be recorded. Many other columns should be added to your dataset based on the particularities of your meta-analysis (e.g., species, response variable, geographic coordinates, etc).</t>
     </r>
+  </si>
+  <si>
+    <t>paired_means</t>
+  </si>
+  <si>
+    <t>pair_type</t>
+  </si>
+  <si>
+    <t>Were the means of groups 1 and 2 paired? E.g., before-after a treatment or the means of spatially paired plots?</t>
+  </si>
+  <si>
+    <t>Were the pairings spatial or temporal? This might be used to justify different values for rho.</t>
+  </si>
+  <si>
+    <t>TRUE or FALSE</t>
+  </si>
+  <si>
+    <t>spatial, temporal</t>
   </si>
 </sst>
 </file>
@@ -1015,9 +1033,29 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
+  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4CE9E0-C701-AD41-BC6C-4A671B2C8E8B}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.83203125" style="42" customWidth="1"/>
@@ -1194,341 +1232,363 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B20" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C20" s="34" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B21" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C21" s="34" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B24" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C24" s="35" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B27" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C27" s="36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="38" t="s">
+    <row r="28" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B28" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C28" s="39" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="38" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B29" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C29" s="41" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="38" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B30" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C30" s="41" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.4">
-      <c r="A30" s="60" t="s">
+    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.4">
+      <c r="A32" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="60"/>
-      <c r="C30" s="60"/>
-    </row>
-    <row r="31" spans="1:3" ht="74" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="61" t="s">
+      <c r="B32" s="60"/>
+      <c r="C32" s="60"/>
+    </row>
+    <row r="33" spans="1:3" ht="74" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-    </row>
-    <row r="32" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21" t="s">
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
+    </row>
+    <row r="34" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="33" t="s">
+      <c r="B34" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C34" s="29" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B35" s="31" t="s">
         <v>80</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="31" t="s">
-        <v>82</v>
       </c>
       <c r="C35" s="31" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="24" t="s">
-        <v>19</v>
+      <c r="A36" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C36" s="31" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.4">
-      <c r="A38" s="60" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.4">
+      <c r="A40" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="60"/>
-      <c r="C38" s="60"/>
-    </row>
-    <row r="39" spans="1:3" ht="116" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="61" t="s">
+      <c r="B40" s="60"/>
+      <c r="C40" s="60"/>
+    </row>
+    <row r="41" spans="1:3" ht="116" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="62"/>
-      <c r="C39" s="62"/>
-    </row>
-    <row r="40" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A40" s="58" t="s">
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
+    </row>
+    <row r="42" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="59" t="s">
+      <c r="B42" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="59" t="s">
+      <c r="C42" s="59" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
+    <row r="43" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A43" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B43" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C43" s="34" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A42" s="22" t="s">
+    <row r="44" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A44" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="34" t="s">
+      <c r="B44" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C44" s="34" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A43" s="23" t="s">
+    <row r="45" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A45" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B43" s="35" t="s">
+      <c r="B45" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C45" s="35" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A44" s="23" t="s">
+    <row r="46" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A46" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="B46" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="35" t="s">
+      <c r="C46" s="35" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="23" t="s">
+    <row r="47" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="35" t="s">
+      <c r="B47" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="35" t="s">
+      <c r="C47" s="35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A46" s="24" t="s">
+    <row r="48" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A48" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B46" s="36" t="s">
+      <c r="B48" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C48" s="36" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A47" s="24" t="s">
+    <row r="49" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A49" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B47" s="36" t="s">
+      <c r="B49" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C47" s="36" t="s">
+      <c r="C49" s="36" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="24" t="s">
+    <row r="50" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A50" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B48" s="36" t="s">
+      <c r="B50" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C50" s="36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A49" s="19" t="s">
+    <row r="51" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A51" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B49" s="37" t="s">
+      <c r="B51" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="37" t="s">
+      <c r="C51" s="37" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="19" t="s">
+    <row r="52" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A52" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B50" s="37" t="s">
+      <c r="B52" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="37" t="s">
+      <c r="C52" s="37" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1536,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D8913A-2DED-E14B-8F03-74C552774659}">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="26" bestFit="1" customWidth="1"/>
@@ -1552,18 +1612,20 @@
     <col min="11" max="11" width="26.1640625" style="29" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.5" style="30" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.1640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.1640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.1640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.83203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8" style="41" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.83203125" style="41"/>
-    <col min="23" max="16384" width="10.83203125" style="25"/>
+    <col min="14" max="14" width="14.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.1640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.1640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" style="41" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.83203125" style="41"/>
+    <col min="25" max="16384" width="10.83203125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1603,31 +1665,37 @@
       <c r="M1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="P1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="Q1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="R1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="24" t="s">
+      <c r="S1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="T1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="24" t="s">
+      <c r="U1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="38" t="s">
+      <c r="V1" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="U1" s="40" t="s">
+      <c r="W1" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="V1" s="40" t="s">
+      <c r="X1" s="40" t="s">
         <v>64</v>
       </c>
     </row>

--- a/data/template_dataset.xlsx
+++ b/data/template_dataset.xlsx
@@ -1033,26 +1033,6 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
-  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
-  <we:alternateReferences>
-    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4CE9E0-C701-AD41-BC6C-4A671B2C8E8B}">
   <dimension ref="A1:D52"/>
